--- a/hyperscale_capex_gpu_analysis.xlsx
+++ b/hyperscale_capex_gpu_analysis.xlsx
@@ -10,7 +10,8 @@
     <sheet name="ROIC Analysis" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Revenue per $1 Capex" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="GPU Allocation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="GPU Rental Revenue" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +56,12 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +86,12 @@
         <bgColor rgb="00548235"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+        <bgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +121,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1136,14 +1149,457 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cloud GPU Rental Revenue: Hyperscale vs Neocloud (External Customers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>External GPU revenue = cloud instances rented to customers (EC2, Azure ML, Vertex AI, CoreWeave, Lambda). Sources: Synergy, ABI Research, company filings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Hyperscale External GPU Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>2023 ($B)</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>2024 ($B)</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>2025E ($B)</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>YoY Growth %</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AWS (Amazon)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Microsoft Azure</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Oracle Cloud</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Total Hyperscale</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Neocloud External GPU Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>2023 ($B)</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>2024 ($B)</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>2025E ($B)</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>YoY Growth %</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>737%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lambda Labs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>333%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Crusoe</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>338%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>460%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>321%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total Neocloud</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>471%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Market Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>2023 ($B)</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>2024 ($B)</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>2025E ($B)</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>2024 Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Hyperscale (AWS, Azure, GCP, Oracle)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Neocloud (CoreWeave, Lambda, etc.)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Total GPU Rental Market</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>14</v>
+      </c>
+      <c r="D26" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Key Insight: Hyperscale dominates 2024 (~71%) but neoclouds growing 200%+ YoY; CoreWeave $1.92B (2024), Synergy projects neoclouds $23B (2025), $180B (2030)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A28:E28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr"/>
+      <c r="A1" s="13" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
@@ -1207,9 +1663,26 @@
       <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Report generated: 2026-02-21 13:31</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>5. GPU RENTAL REVENUE: Hyperscale external GPU ~$10B (2024), neocloud ~$4B. Hyperscale 71% share;</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   neoclouds growing 200%+ YoY (CoreWeave $1.92B). Synergy: neoclouds $23B (2025), $180B (2030).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Report generated: 2026-02-21 13:40</t>
         </is>
       </c>
     </row>

--- a/hyperscale_capex_gpu_analysis.xlsx
+++ b/hyperscale_capex_gpu_analysis.xlsx
@@ -52,13 +52,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -922,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -930,12 +930,14 @@
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hyperscale GPU Allocation: Internal vs External Consumption</t>
+          <t>GPU Allocation: Internal vs External Consumption</t>
         </is>
       </c>
     </row>
@@ -964,15 +966,20 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
+          <t>External GPU Revenue ($B)</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
           <t>Internal Use Cases</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>External Use Cases</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Est. GPU Count (2024)</t>
         </is>
@@ -990,17 +997,20 @@
       <c r="C5" t="n">
         <v>45</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Recommendation engines, fulfillment AI, Alexa</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>EC2 GPU instances, SageMaker, Bedrock</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>~500K</t>
         </is>
@@ -1018,17 +1028,20 @@
       <c r="C6" t="n">
         <v>35</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Copilot, Office AI, Bing, internal ML</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Azure ML, OpenAI API, GPU VMs</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>~485K</t>
         </is>
@@ -1046,17 +1059,20 @@
       <c r="C7" t="n">
         <v>30</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Search, YouTube, Gemini, internal AI</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Vertex AI, GPU VMs, Gemini API</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>~400K</t>
         </is>
@@ -1074,17 +1090,20 @@
       <c r="C8" t="n">
         <v>15</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Feed ranking, Reels, Llama, internal AI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Limited (Meta Cloud)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>~600K</t>
         </is>
@@ -1102,31 +1121,233 @@
       <c r="C9" t="n">
         <v>40</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Database AI, Fusion Apps, internal workloads</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>OCI GPU instances, GenAI cloud</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>~100K</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Aggregate: ~65% internal / 35% external across Big 5 hyperscalers</t>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Neocloud Vendors (100% external)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Internal %</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>External %</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>External GPU Revenue ($B)</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Internal Use Cases</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>External Use Cases</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Est. GPU Count (2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>GPU cloud for AI training, inference</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>~50K</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lambda Labs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>GPU instances, ML training</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>~20K</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Crusoe</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>GPU cloud, flaring mitigation compute</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>~15K</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GPU cloud, sovereign AI</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>~10K</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Total Neocloud</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>100</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>~95K</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Hyperscale aggregate: ~65% internal / 35% external. Neoclouds: 100% external, ~$4B revenue (2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Source: Industry estimates; Meta/Google skew internal (ads/search); AWS/Azure/Oracle skew external (cloud revenue)</t>
         </is>
@@ -1134,10 +1355,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1174,7 +1395,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Hyperscale External GPU Revenue</t>
         </is>
@@ -1313,7 +1534,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Neocloud External GPU Revenue</t>
         </is>
@@ -1473,7 +1694,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Market Summary</t>
         </is>
@@ -1682,7 +1903,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Report generated: 2026-02-21 13:40</t>
+          <t>Report generated: 2026-02-21 13:45</t>
         </is>
       </c>
     </row>

--- a/hyperscale_capex_gpu_analysis.xlsx
+++ b/hyperscale_capex_gpu_analysis.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,11 +57,15 @@
     </font>
     <font>
       <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +92,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="007030A0"/>
         <bgColor rgb="007030A0"/>
       </patternFill>
@@ -105,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,7 +132,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -922,29 +938,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GPU Allocation: Internal vs External Consumption</t>
+          <t>Hyperscale GPU Allocation: Internal vs External Consumption</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Internal = own AI products (Copilot, Gemini, Llama, recommendations). External = cloud GPU instances for customers.</t>
+          <t>Internal = own AI products. External = cloud GPU instances for customers. External % derived from revenue &amp; assumptions below.</t>
         </is>
       </c>
     </row>
@@ -966,20 +980,15 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>External GPU Revenue ($B)</t>
+          <t>Internal Use Cases</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Internal Use Cases</t>
+          <t>External Use Cases</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>External Use Cases</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Est. GPU Count (2024)</t>
         </is>
@@ -992,25 +1001,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55</v>
+        <v>44.9</v>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.8</v>
+        <v>55.1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Recommendation engines, fulfillment AI, Alexa</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recommendation engines, fulfillment AI, Alexa</t>
+          <t>EC2 GPU instances, SageMaker, Bedrock</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
-        <is>
-          <t>EC2 GPU instances, SageMaker, Bedrock</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>~500K</t>
         </is>
@@ -1023,25 +1029,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>47.7</v>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.5</v>
+        <v>52.3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Copilot, Office AI, Bing, internal ML</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Copilot, Office AI, Bing, internal ML</t>
+          <t>Azure ML, OpenAI API, GPU VMs</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>Azure ML, OpenAI API, GPU VMs</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>~485K</t>
         </is>
@@ -1054,25 +1057,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>60.1</v>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.2</v>
+        <v>39.9</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Search, YouTube, Gemini, internal AI</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Search, YouTube, Gemini, internal AI</t>
+          <t>Vertex AI, GPU VMs, Gemini API</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>Vertex AI, GPU VMs, Gemini API</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>~400K</t>
         </is>
@@ -1085,25 +1085,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>98.8</v>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Feed ranking, Reels, Llama, internal AI</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Feed ranking, Reels, Llama, internal AI</t>
+          <t>Limited (Meta Cloud)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>Limited (Meta Cloud)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>~600K</t>
         </is>
@@ -1116,25 +1113,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>63.8</v>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.5</v>
+        <v>36.2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Database AI, Fusion Apps, internal workloads</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Database AI, Fusion Apps, internal workloads</t>
+          <t>OCI GPU instances, GenAI cloud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
-        <is>
-          <t>OCI GPU instances, GenAI cloud</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>~100K</t>
         </is>
@@ -1143,222 +1137,217 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Neocloud Vendors (100% external)</t>
+          <t>Assumptions (Rental Revenue Model)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Internal %</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>External %</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>External GPU Revenue ($B)</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Internal Use Cases</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>External Use Cases</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>Est. GPU Count (2024)</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rental rate per GPU-hour:</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>$3.50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>GPU cloud for AI training, inference</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>~50K</t>
+          <t>Utilization (billable hours / available hours):</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>45%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lambda Labs</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>GPU instances, ML training</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>~20K</t>
+          <t>Hours per year:</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8,760</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Crusoe</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>GPU cloud, flaring mitigation compute</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>~15K</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Nebius</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>100</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>GPU cloud, sovereign AI</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>~10K</t>
+          <t>Source: Blended H100/A100 rates (Atlas, Vast.ai, cloud providers); industry utilization ~40-50%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Total Neocloud</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>100</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>~95K</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Hyperscale aggregate: ~65% internal / 35% external. Neoclouds: 100% external, ~$4B revenue (2024)</t>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>External % Calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Formula: External % = External GPU Revenue / (GPU Count × Hours/Year × Utilization × Rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rearranged: External GPU Revenue = GPU Count × External % × 8,760 × Utilization × Rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Source: Industry estimates; Meta/Google skew internal (ads/search); AWS/Azure/Oracle skew external (cloud revenue)</t>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>GPU Count</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>External % (calc)</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Revenue ($B) (calc)</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Revenue ($B) (reported)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Amazon (AWS)</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Microsoft (Azure)</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>485000</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Google (GCP)</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>600000</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Aggregate: ~65% internal / 35% external across Big 5 hyperscalers</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Source: External % derived from reported GPU rental revenue; GPU counts from industry estimates</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1402,27 +1391,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>2023 ($B)</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>2024 ($B)</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>2025E ($B)</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>YoY Growth %</t>
         </is>
@@ -1541,27 +1530,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2023 ($B)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>2024 ($B)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>2025E ($B)</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>YoY Growth %</t>
         </is>
@@ -1701,27 +1690,27 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Segment</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>2023 ($B)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>2024 ($B)</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>2025E ($B)</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>2024 Share</t>
         </is>
@@ -1820,7 +1809,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr"/>
+      <c r="A1" s="19" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
@@ -1903,7 +1892,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Report generated: 2026-02-21 13:45</t>
+          <t>Report generated: 2026-02-21 13:57</t>
         </is>
       </c>
     </row>
